--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dccf2233d3cc742</t>
+          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Developer with AWS-1</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f612381d18aae353</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfc8635935e24293</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-3</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b7205d508ead07</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LIBERTY Dental Plan</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Kimball, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5067351d4fc731d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Delivery Platform Software Engineer 1 - Developer Tools Team (Hybrid - Seattle, WA)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea2d4097cba0a88</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MLOps, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89ca98429cd4ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Insight IT Pty</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cf4737c1f0453e9</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,69 +2026,69 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6f5901eac2e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Software Engineer III - ML</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>GCP GKE- Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, Oracle, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172cf84d3f86a04</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>.Enterprise Architect (Contract)</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>.Enterprise Architect (Contract)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,52 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9563a5d4e36f2b7a</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69bace1ccc12c172</t>
+          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3e309eb21ff0bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,11 +2267,11 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Software Engineer III - ML</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GCP GKE- Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d14612c204824</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>.Enterprise Architect (Contract)</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>AWS Full Stack React Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>.Enterprise Architect (Contract)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c58c20e2b53fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
@@ -1938,52 +1938,52 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b07448a9af704</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Software Engineer III - ML</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=164e35c8e4519a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>AWS Full Stack React Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>.Enterprise Architect (Contract)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>.Enterprise Architect (Contract)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3295,76 +3295,6 @@
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Databricks, Kafka, Splunk, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5916fa5737d5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,29 +941,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Software Engineer III - ML</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Software Engineer III - ML</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>AWS Full Stack React Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>.Enterprise Architect (Contract)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>.Enterprise Architect (Contract)</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
@@ -3227,76 +3227,6 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff122e6a11cd0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,29 +906,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Sr Software Engineer (Java, Streaming)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Software Engineer II (Java, Streaming)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Data Software Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Software Engineer III - ML</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346865856cd824d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
@@ -2468,20 +2468,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da775dac4a2cc346</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d66bbd4baf507c67</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0869394e4881bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Full Stack React Developer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>.Enterprise Architect (Contract)</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,287 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS (Snowflake)</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bcfb79ed1af62a</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps / API Engineer — Mid-Level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Nomad Temporary Housing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,29 +906,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Java, Streaming)</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a372f8c9082d5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java, Streaming)</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Dataflow, Zookeeper, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16644732acad479c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Software Engineer III</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e9f7eb8238e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2801,29 +2801,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,77 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Resiliency and Recovery Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Databricks AI Developer / Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GHK Technologies Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee350682361d2f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Intellitech llc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2871,29 +2871,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intellitech llc</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Medallion Architecture, Scala, MongoDB, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cd148978fc2ece</t>
+          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2980,41 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks AI Developer / Architect</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GHK Technologies Inc.</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Delta Live Tables, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f146b67b9249aaee</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2980,6 +2980,41 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,60 +818,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps / API Engineer — Mid-Level</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nomad Temporary Housing</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Blob Storage, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e41e92d4cf6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, Dimension Tables</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822de5b31b41394f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Senior Full Stack Developer - POS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Intralot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,85 +2936,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8cdec8520bfcab</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Healthcare (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,85 +2866,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdc232102958f84</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
+          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,94 +776,94 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - POS</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Event Hubs, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371ed48c15d1706b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intralot</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c50badab80eaaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,77 +1151,77 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Saviynt Security Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Information Protection Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Innovien Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9369de31486590d</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d360025ad1e8d3</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Healthcare (Remote)</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Azure, GCP, Spark, Scala, Airflow</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54f977f3210b68</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2665,216 +2665,6 @@
         </is>
       </c>
       <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f646fb7199ae18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
         </is>
       </c>
     </row>
@@ -718,20 +718,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,94 +741,94 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Saviynt Security Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4eb69ebcacfd269</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Information Protection Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e07b03adcd1968f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e9d01fa2d64178c</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Dataflow, Oracle, SQL Server, PostgreSQL, MySQL, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4fe49e1b757831</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944f922dade04119</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2420,251 +2420,6 @@
         </is>
       </c>
       <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f6e0cadd7e964a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Acquisition)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a2376d63bc21df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c571fa26321ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Corporate AI and Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>NewCourse Communications</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7cd05c20de1f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer – AI &amp; Cloud Platforms – Nearshore</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Innovien Solutions</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9b6ed746664268</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd986335447e67</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2280,146 +2280,6 @@
         </is>
       </c>
       <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae7236a6d23f32f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Oozie, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d79ae6e8911cec</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Analyst / Programmer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Date Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Primrose Schools</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Software Engineer - Career</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e60b0d6d032f03</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Corporate AI and Machine Learning Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Dimension Tables, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75c774b709e20c3</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NewCourse Communications</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Scala, SQL Server, Splunk, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109deef0eb13765e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1996,29 +1996,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2105,181 +2105,6 @@
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=220d00b675eb18d6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Career</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00569d3fe30ccfef</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Developer Salesforce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Freeway Psychiatry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Resiliency and Recovery Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
+          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Resiliency and Recovery Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
+          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,85 +2026,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analyst / Programmer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Dataflow, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532d80ca272af0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Date Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primrose Schools</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef71651c5aceb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,77 +871,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Developer Salesforce</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Freeway Psychiatry</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd64d1c32ba1de8</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Helixtachinc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Fullstack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,227 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Resiliency and Recovery Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f04ba60584c2ed0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79fc3a4f134e9a9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Hadoop, Spark, Scala, Snowflake, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b8523ec10ba432</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f55092532d7ddf1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I4DM</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Data Factory</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,84 +601,84 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb98a0e64bd00ece</t>
+          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb767017596ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Sterling, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball, Star Schema</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,73 +692,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fa3a57e58f1e08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Helixtachinc</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e6f748f71d699e</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Fullstack Developer</t>
+          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f06667bcfd75b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>Data Engineer - TechCare Operations: Blueprint team</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ceb16fbcac8b21d</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API Dev + CI/CD)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc3ae2a8608fdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End/Full Stack (Docker/Containerization, Python on AWS, React, API De</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Sarah Cannon Research Institute</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c45b67fc2b62b74</t>
+          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - TechCare Operations: Blueprint team</t>
+          <t>Resiliency &amp; Recovery Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, MapReduce, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c037761cc3f6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
+          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Full Stack React Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>.Enterprise Architect (Contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>ML Engineer / AI Operations-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,50 +1781,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>

--- a/results/job_matches_2026-04-04.xlsx
+++ b/results/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Data, Analytics &amp; AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sterling, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25992fcd2fc606d1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4891b06f58ff08</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eightfold</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SQS, SNS, RDS, Azure, GCP, Spark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vision Technologies, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Glen Burnie, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL / Python Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, Jenkins, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ETL / Python Developer</t>
+          <t>Data Analytics Engineer, Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc9093da7a5e35</t>
+          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer, Senior</t>
+          <t>C# and Azure Cloud - Software Development Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7454873b519feaba</t>
+          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C# and Azure Cloud - Software Development Engineer II</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482d9cbc7cb63ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Parts Authority</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Kafka, PostgreSQL, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
+          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Republic Finance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e2eef595df2ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Intern</t>
+          <t>FLEX Customer 360, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Republic Finance</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8b3947ebdce760</t>
+          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Hive, Spark, Scala, Snowflake, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, ELT, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370caed2dea48a3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, GCP, Spark, Scala, NoSQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sarah Cannon Research Institute</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced70cae485e9d61</t>
+          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,297 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729488692c54a957</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87fe175222dffef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=70ca01249d0f4376</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8645b0d44909612d</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AWS Full Stack React Developer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3db65c20ad4663ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>.Enterprise Architect (Contract)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Transmedics</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Andover, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, IAM, RDS, Scala, Oracle, Data Modeling, ETL, ELT, Git</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9d4882bd119809</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ML Engineer / AI Operations-2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
         </is>
       </c>
     </row>
